--- a/Test Data - 01.02.2026.xlsx
+++ b/Test Data - 01.02.2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Sanjay Github\Data-Analytics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Sanjay_Github\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894AFDC8-F591-4617-BBB6-1359DD5B6BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB78ADD-916F-460D-B842-7A681C622825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{DF4A2310-D878-4A86-A515-C029D05513CC}"/>
   </bookViews>
